--- a/Documentation/Savr_App Software Estimation Document Ver. 1.0.docx.xlsx
+++ b/Documentation/Savr_App Software Estimation Document Ver. 1.0.docx.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Freelance\INVIOS\CODE\savr-app\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Freelance\INVIOS\Assignment\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B326B4-1184-4418-B21D-F835F3B5BE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5F31FB-CC86-417C-B865-F44FEC424583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8D19311-4A29-4A84-8AF6-817719B6CBFC}"/>
   </bookViews>
@@ -151,7 +151,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,6 +161,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -177,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -208,6 +214,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -561,7 +571,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="12">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -569,7 +579,7 @@
         <v>7</v>
       </c>
       <c r="D4" s="12">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -577,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -585,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="12">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -593,7 +603,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="12">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -601,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -609,7 +619,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -633,7 +643,7 @@
         <v>12</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -650,7 +660,10 @@
         <v>18</v>
       </c>
       <c r="D14" s="12">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="E14">
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -660,7 +673,7 @@
         <v>19</v>
       </c>
       <c r="D15" s="12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -670,7 +683,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -680,7 +693,10 @@
         <v>21</v>
       </c>
       <c r="D17" s="12">
-        <v>4</v>
+        <v>0.5</v>
+      </c>
+      <c r="E17">
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -690,7 +706,10 @@
         <v>17</v>
       </c>
       <c r="D18" s="12">
-        <v>1</v>
+        <v>0.25</v>
+      </c>
+      <c r="E18">
+        <v>0.25</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -700,7 +719,7 @@
         <v>15</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="9"/>
     </row>
@@ -711,7 +730,7 @@
         <v>14</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -735,7 +754,10 @@
         <v>12</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="E23">
+        <v>0.1</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -749,7 +771,10 @@
         <v>24</v>
       </c>
       <c r="D25" s="12">
-        <v>2</v>
+        <v>0.5</v>
+      </c>
+      <c r="E25">
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -759,7 +784,10 @@
         <v>26</v>
       </c>
       <c r="D26" s="12">
-        <v>1</v>
+        <v>0.25</v>
+      </c>
+      <c r="E26">
+        <v>0.3</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -769,7 +797,10 @@
         <v>25</v>
       </c>
       <c r="D27" s="12">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="E27">
+        <v>0.3</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -779,7 +810,10 @@
         <v>27</v>
       </c>
       <c r="D28" s="12">
-        <v>1</v>
+        <v>0.25</v>
+      </c>
+      <c r="E28">
+        <v>0.2</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -787,7 +821,10 @@
         <v>28</v>
       </c>
       <c r="D29" s="12">
-        <v>4</v>
+        <v>0.5</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -797,7 +834,7 @@
         <v>23</v>
       </c>
       <c r="D30" s="12">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -807,7 +844,7 @@
         <v>15</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -817,49 +854,52 @@
         <v>14</v>
       </c>
       <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C38" s="13" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="E35">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C38" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="14">
         <f>SUM(D3:D35)</f>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C39" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C39" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="14">
         <f>SUM(E3:E35)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
